--- a/data-raw/codigosPoder.xlsx
+++ b/data-raw/codigosPoder.xlsx
@@ -1,21 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DCGF\Gitlab\loa\bancos\manual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DD3DFF9D6CE0D9D93C06F1D444A14FE59B7E8FD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="45" windowWidth="22995" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="45" windowWidth="22995" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
-    <sheet name="Plan2" sheetId="2" r:id="rId2"/>
-    <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -64,8 +61,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,9 +111,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -154,9 +151,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -191,7 +188,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -226,7 +223,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -399,15 +396,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,7 +412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -423,7 +420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -431,7 +428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -439,7 +436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -447,7 +444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -460,27 +457,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -739,34 +738,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0637625-725E-468F-9F3F-264036A807CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8EE00F8-1D4A-4AE4-91A3-857FDA768692}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D35AE395-48CC-4CD1-97DC-51D6C3565C0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D35AE395-48CC-4CD1-97DC-51D6C3565C0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8EE00F8-1D4A-4AE4-91A3-857FDA768692}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D013A1C7-98FA-4B26-B1BB-6BB2F84B017E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>